--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565492465</v>
+        <v>46157.93089064964</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93089064964</v>
+        <v>46157.93166972025</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93166972025</v>
+        <v>46157.93397482955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397482955</v>
+        <v>46157.93715178061</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715178061</v>
+        <v>46158.28213887424</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213887424</v>
+        <v>46158.29675222623</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675222623</v>
+        <v>46158.29811839107</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811839107</v>
+        <v>46158.33384747546</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384747546</v>
+        <v>46158.36854128779</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854128779</v>
+        <v>46158.3728490291</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
